--- a/assessment_forms/008_financial_behavior_assessment--assessment_forms.xlsx
+++ b/assessment_forms/008_financial_behavior_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'annual'}</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Annual'}</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'housing'}</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Housing'}</t>
+          <t>Housing</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'transportation'}</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Transportation'}</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'clothing'}</t>
+          <t>clothing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Clothing'}</t>
+          <t>Clothing</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'credit_union'}</t>
+          <t>credit_union</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Union'}</t>
+          <t>Credit Union</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_app'}</t>
+          <t>mobile_app</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile App'}</t>
+          <t>Mobile App</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Friends'}</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'financial_advisor'}</t>
+          <t>financial_advisor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Financial Advisor'}</t>
+          <t>Financial Advisor</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'books'}</t>
+          <t>books</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Books'}</t>
+          <t>Books</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'online_courses'}</t>
+          <t>online_courses</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Online Courses'}</t>
+          <t>Online Courses</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'workshops'}</t>
+          <t>workshops</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Workshops'}</t>
+          <t>Workshops</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'credit_union'}</t>
+          <t>credit_union</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Union'}</t>
+          <t>Credit Union</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_app'}</t>
+          <t>mobile_app</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile App'}</t>
+          <t>Mobile App</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'short_term'}</t>
+          <t>short_term</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Short Term'}</t>
+          <t>Short Term</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'medium_term'}</t>
+          <t>medium_term</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Medium Term'}</t>
+          <t>Medium Term</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'long_term'}</t>
+          <t>long_term</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Long Term'}</t>
+          <t>Long Term</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
